--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487005_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487005_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1786</v>
+        <v>7.7418</v>
       </c>
       <c r="E2" t="n">
         <v>7.876</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6974</v>
+        <v>-0.1342</v>
       </c>
       <c r="G2" t="n">
         <v>6.7795</v>
@@ -610,13 +610,13 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8678</v>
+        <v>-1.3046</v>
       </c>
       <c r="T2" t="n">
         <v>-0.9494</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9184</v>
+        <v>-0.3552</v>
       </c>
       <c r="V2" t="n">
         <v>0.8295</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.188</v>
+        <v>4.8314</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6764</v>
+        <v>3.964</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.8673</v>
       </c>
       <c r="G3" t="n">
         <v>4.3696</v>
@@ -688,13 +688,13 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>1.531</v>
+        <v>0.1743</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1693</v>
+        <v>0.4569</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6383</v>
+        <v>-0.2826</v>
       </c>
       <c r="V3" t="n">
         <v>0.6982</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5934</v>
+        <v>2.1833</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2712</v>
+        <v>0.1278</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3222</v>
+        <v>2.0555</v>
       </c>
       <c r="G4" t="n">
         <v>1.6499</v>
@@ -766,13 +766,13 @@
         <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.077</v>
+        <v>-0.4871</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2521</v>
+        <v>-0.3954</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1751</v>
+        <v>-0.0917</v>
       </c>
       <c r="V4" t="n">
         <v>1.6366</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3585</v>
+        <v>0.7556</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.7704</v>
+        <v>-2.0769</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1289</v>
+        <v>2.8325</v>
       </c>
       <c r="G5" t="n">
         <v>1.2917</v>
@@ -844,13 +844,13 @@
         <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9413</v>
+        <v>-0.5443</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1857</v>
+        <v>-0.4922</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2444</v>
+        <v>-0.0521</v>
       </c>
       <c r="V5" t="n">
         <v>0.8295</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3975</v>
+        <v>0.151</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1792</v>
+        <v>0.5201</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5766</v>
+        <v>-0.3692</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2422</v>
@@ -922,13 +922,13 @@
         <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7097</v>
+        <v>-1.1613</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9222</v>
+        <v>-0.5813</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7875</v>
+        <v>-0.58</v>
       </c>
       <c r="V6" t="n">
         <v>0.9384</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2161</v>
+        <v>-1.1206</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3226</v>
+        <v>-2.2567</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1064</v>
+        <v>1.1361</v>
       </c>
       <c r="G7" t="n">
         <v>0.2828</v>
@@ -1000,13 +1000,13 @@
         <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0883</v>
+        <v>-0.9928</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1198</v>
+        <v>-1.054</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0315</v>
+        <v>0.0612</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9588</v>
+        <v>-1.696</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.4102</v>
+        <v>-3.8213</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4514</v>
+        <v>2.1253</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1527</v>
@@ -1078,13 +1078,13 @@
         <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1819</v>
+        <v>-0.9191</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.9762</v>
+        <v>-1.3873</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7943</v>
+        <v>0.4682</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8295</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1731</v>
+        <v>-2.4909</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.586</v>
+        <v>-3.3109</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4128</v>
+        <v>0.82</v>
       </c>
       <c r="G9" t="n">
         <v>-0.08500000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>1.6427</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5461</v>
+        <v>-0.8639</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2516</v>
+        <v>-0.9765</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7055</v>
+        <v>0.1126</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7207</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3829</v>
+        <v>-2.5067</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9837</v>
+        <v>-2.4336</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3992</v>
+        <v>-0.0731</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0269</v>
@@ -1234,13 +1234,13 @@
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8283</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1198</v>
+        <v>-0.5697</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7085</v>
+        <v>-0.3824</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3491</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.190100000000001</v>
+        <v>7.8489</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.070099999999999</v>
+        <v>-1.4115</v>
       </c>
       <c r="F11" t="n">
-        <v>9.2601</v>
+        <v>9.260200000000001</v>
       </c>
       <c r="G11" t="n">
         <v>11.8667</v>
@@ -1312,13 +1312,13 @@
         <v>12.3206</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.7094</v>
+        <v>-7.0509</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.6075</v>
+        <v>-5.9489</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1019</v>
+        <v>-1.102</v>
       </c>
       <c r="V11" t="n">
         <v>3.0329</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.5586</v>
+        <v>5.8107</v>
       </c>
       <c r="E12" t="n">
-        <v>4.3746</v>
+        <v>3.5377</v>
       </c>
       <c r="F12" t="n">
-        <v>2.184</v>
+        <v>2.2729</v>
       </c>
       <c r="G12" t="n">
         <v>2.1841</v>
@@ -1390,13 +1390,13 @@
         <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6012</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4607</v>
+        <v>-0.3761</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1405</v>
+        <v>1.2294</v>
       </c>
       <c r="V12" t="n">
         <v>1.1306</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>O. BIESHAAR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.298</v>
+        <v>2.5357</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6035</v>
+        <v>1.3278</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3056</v>
+        <v>1.2079</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1176</v>
+        <v>2.3262</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5256</v>
+        <v>2.8446</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.592</v>
+        <v>-0.5184</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5969</v>
+        <v>3.0513</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6103</v>
+        <v>1.9466</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0134</v>
+        <v>1.1047</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7144</v>
+        <v>-0.7251</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1358</v>
+        <v>0.898</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5786</v>
+        <v>-1.6231</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0267</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4369</v>
+        <v>0.7216</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0067</v>
+        <v>-0.3024</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4302</v>
+        <v>1.0241</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.048</v>
+        <v>1.1306</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.048</v>
+        <v>-0.5285</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. BIESHAAR</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0982</v>
+        <v>1.5657</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3864</v>
+        <v>1.8713</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7118</v>
+        <v>-0.3056</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3262</v>
+        <v>-1.1176</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8446</v>
+        <v>-0.5256</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5184</v>
+        <v>-0.592</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0513</v>
+        <v>0.5969</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9466</v>
+        <v>0.6103</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1047</v>
+        <v>-0.0134</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7251</v>
+        <v>-1.7144</v>
       </c>
       <c r="N14" t="n">
-        <v>0.898</v>
+        <v>-1.1358</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.6231</v>
+        <v>-0.5786</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2841</v>
+        <v>1.7046</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2438</v>
+        <v>1.2745</v>
       </c>
       <c r="U14" t="n">
-        <v>1.528</v>
+        <v>0.4302</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1306</v>
+        <v>-0.048</v>
       </c>
       <c r="W14" t="n">
-        <v>1.6591</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5285</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5412</v>
+        <v>-1.4223</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1698</v>
+        <v>-1.5907</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.1684</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.702</v>
+        <v>1.798</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4156</v>
+        <v>1.0742</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.2864</v>
+        <v>0.7238</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.6933</v>
+        <v>3.1653</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4122</v>
+        <v>3.0469</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.1055</v>
+        <v>0.1184</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0087</v>
+        <v>-1.3673</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8278</v>
+        <v>-1.9727</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1809</v>
+        <v>0.6054</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R15" t="n">
         <v>1.0267</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8166</v>
+        <v>0.6963</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1581</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6586</v>
+        <v>0.6268</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3708</v>
+        <v>-1.8633</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4189</v>
+        <v>-1.7454</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.048</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7518</v>
+        <v>-1.8663</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.0091</v>
+        <v>-1.902</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2573</v>
+        <v>0.0357</v>
       </c>
       <c r="G16" t="n">
-        <v>1.798</v>
+        <v>-3.702</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0742</v>
+        <v>-0.4156</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7238</v>
+        <v>-3.2864</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1653</v>
+        <v>-1.6933</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0469</v>
+        <v>0.4122</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1184</v>
+        <v>-2.1055</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3673</v>
+        <v>-2.0087</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9727</v>
+        <v>-0.8278</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6054</v>
+        <v>-1.1809</v>
       </c>
       <c r="P16" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-2.0534</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-3.0801</v>
       </c>
       <c r="R16" t="n">
         <v>1.0267</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3669</v>
+        <v>1.4916</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3489</v>
+        <v>0.4258</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7157</v>
+        <v>1.0657</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8633</v>
+        <v>1.3708</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.7454</v>
+        <v>1.4189</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1179</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="17">
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.8016</v>
+        <v>-2.2786</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.2187</v>
+        <v>-2.6957</v>
       </c>
       <c r="F17" t="n">
         <v>0.4171</v>
@@ -1780,10 +1780,10 @@
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1395</v>
+        <v>0.3835</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7246</v>
+        <v>-0.2016</v>
       </c>
       <c r="U17" t="n">
         <v>0.5851</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.0906</v>
+        <v>-3.2932</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.5653</v>
+        <v>-2.9354</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4747</v>
+        <v>-0.3578</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.0008</v>
+        <v>-3.5553</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0772</v>
+        <v>0.2238</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.9235</v>
+        <v>-3.7791</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.068</v>
+        <v>-1.7965</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3046</v>
+        <v>0.9412</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.7633</v>
+        <v>-2.7376</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9328</v>
+        <v>-1.7589</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7726</v>
+        <v>-0.7174</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1602</v>
+        <v>-1.0415</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3102</v>
+        <v>-0.188</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4453</v>
+        <v>-0.7015</v>
       </c>
       <c r="U18" t="n">
-        <v>0.865</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.2214</v>
+        <v>-0.1659</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.9159</v>
+        <v>0.5893</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3055</v>
+        <v>-0.7552</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SUÁREZ CUSTODIO</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1635</v>
+        <v>-3.9267</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9942</v>
+        <v>-4.4607</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1693</v>
+        <v>0.534</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.7622</v>
+        <v>-4.0008</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0277</v>
+        <v>-1.0772</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7345</v>
+        <v>-2.9235</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.7766</v>
+        <v>-3.068</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6443</v>
+        <v>-0.3046</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1322</v>
+        <v>-2.7633</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9856</v>
+        <v>-0.9328</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3833</v>
+        <v>-0.7726</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.1602</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7239</v>
+        <v>1.4741</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7823</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0584</v>
+        <v>0.9242</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.3573</v>
+        <v>-2.2214</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.9159</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3573</v>
+        <v>-1.3055</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>P. SUÁREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.7961</v>
+        <v>-4.3151</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6676</v>
+        <v>-2.4126</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1285</v>
+        <v>-1.9025</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.5553</v>
+        <v>-3.7622</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2238</v>
+        <v>-2.0277</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.7791</v>
+        <v>-1.7345</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7965</v>
+        <v>-2.7766</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9412</v>
+        <v>-1.6443</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.7376</v>
+        <v>-1.1322</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7589</v>
+        <v>-0.9856</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7174</v>
+        <v>-0.3833</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0415</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6909</v>
+        <v>0.5723</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4337</v>
+        <v>0.3639</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2571</v>
+        <v>0.2084</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1659</v>
+        <v>-2.3573</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7552</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.19</v>
+        <v>-7.1901</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.260200000000001</v>
+        <v>-9.260300000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>2.07</v>
+        <v>2.0701</v>
       </c>
       <c r="G21" t="n">
         <v>-11.8667</v>
@@ -2065,25 +2065,25 @@
         <v>-13.8282</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.405000000000001</v>
+        <v>-1.404999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>7.335000000000001</v>
+        <v>7.334999999999998</v>
       </c>
       <c r="L21" t="n">
-        <v>-8.739700000000001</v>
+        <v>-8.739699999999999</v>
       </c>
       <c r="M21" t="n">
         <v>-10.4617</v>
       </c>
       <c r="N21" t="n">
-        <v>-5.373200000000001</v>
+        <v>-5.3732</v>
       </c>
       <c r="O21" t="n">
-        <v>-5.088500000000001</v>
+        <v>-5.0885</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0001000000000001</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q21" t="n">
         <v>-12.3204</v>
@@ -2092,22 +2092,22 @@
         <v>12.3205</v>
       </c>
       <c r="S21" t="n">
-        <v>7.7094</v>
+        <v>7.709300000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1021</v>
+        <v>1.102</v>
       </c>
       <c r="U21" t="n">
-        <v>6.607600000000001</v>
+        <v>6.6075</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.032899999999999</v>
+        <v>-3.0329</v>
       </c>
       <c r="W21" t="n">
-        <v>3.363200000000001</v>
+        <v>3.3632</v>
       </c>
       <c r="X21" t="n">
-        <v>-6.396</v>
+        <v>-6.396000000000001</v>
       </c>
     </row>
   </sheetData>
